--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_backtest_metrics.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parameters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'performance'!$A$1:$C$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'parameters'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'parameters'!$A$1:$C$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -517,7 +517,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2021-02-01至2025-12-31</t>
+          <t>2021-02-01至2026-07-31</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1192</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.945882042156287</v>
+        <v>3.092729715756673</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.05411795784370599</v>
+        <v>2.092729715756698</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.01169336591816683</v>
+        <v>0.2383320027124176</v>
       </c>
     </row>
     <row r="8">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.2355315735470571</v>
+        <v>0.2699401603746709</v>
       </c>
     </row>
     <row r="9">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.004391567163994948</v>
+        <v>0.8717522448455248</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.006280684007051932</v>
+        <v>1.302490318261337</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4954915654658095</v>
+        <v>0.274094394510775</v>
       </c>
     </row>
     <row r="12">
@@ -669,7 +669,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2024年09月</t>
+          <t>2024年10月-2025年04月</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.02359952566937027</v>
+        <v>0.8695252711672966</v>
       </c>
     </row>
     <row r="14">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>60.40662590726951</v>
+        <v>54.83946747285091</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.2399100998276266</v>
+        <v>0.2177805561712748</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.4359958725014025</v>
+        <v>0.4405202727214984</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>3.861577181208053</v>
+        <v>1.26671675432006</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1192</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="19">
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -965,191 +965,289 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>交易设置</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>调仓间隔 Δt</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>1</v>
+          <t>调仓模式</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>rebalance</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>交易设置</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>初始净值 NAV₀</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
+          <t>组合结构</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>单账户每1个交易日全组合调仓</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>收益参数</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>年化无风险利率 r_f</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.015</v>
+          <t>账户数量</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>买入成本 c_buy</t>
+          <t>每账户初始资金比例</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>卖出成本 c_sell</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0.001</v>
+          <t>计划调仓账户数</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>计划调仓日1个，其他交易日0个</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>完整换仓成本 T_c</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.002</v>
+          <t>单账户调仓间隔（交易日）</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>账户结构</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>当日成交额使用比例 ρ_amt</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>0.1</v>
+          <t>账户之间资金转移</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>不适用；单账户</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>交易设置</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>倒序分位 q_desc</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>0.95</v>
+          <t>初始净值 NAV₀</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>收益参数</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>等价升序分位 q_asc</t>
+          <t>年化无风险利率 r_f</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>组合约束</t>
+          <t>交易成本</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>指数权重</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>按过滤前计划入选数量等权</t>
-        </is>
+          <t>买入成本 c_buy</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>收益口径</t>
+          <t>交易成本</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>扣费后收益</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>买入和卖出均扣除交易成本</t>
-        </is>
+          <t>卖出成本 c_sell</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>交易成本</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>完整换仓成本 T_c</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>容量参数</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>当日成交额使用比例 ρ_amt</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>容量参数</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>倒序分位 q_desc</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>容量参数</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>等价升序分位 q_asc</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>组合约束</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>指数权重</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>按过滤前计划入选数量等权</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>收益口径</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>扣费后收益</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>买入和卖出均扣除交易成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>容量口径</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>组合容量</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>各持仓ETF容量的5%分位</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C22"/>
+  <autoFilter ref="A1:C28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>